--- a/testdata/data.xlsx
+++ b/testdata/data.xlsx
@@ -26,7 +26,7 @@
     <t>Eve</t>
   </si>
   <si>
-    <t>15</t>
+    <t>13</t>
   </si>
   <si>
     <t>NO</t>
